--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104594_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104594_W16.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8553</v>
+        <v>6.3587</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1512</v>
+        <v>5.5255</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3684</v>
+        <v>7.3626</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1383</v>
+        <v>3.1446</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2301</v>
+        <v>4.2181</v>
       </c>
       <c r="J2" t="n">
-        <v>8.025499999999999</v>
+        <v>7.9909</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0304</v>
+        <v>3.0164</v>
       </c>
       <c r="L2" t="n">
-        <v>4.995</v>
+        <v>4.9744</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.657</v>
+        <v>-0.6282</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1079</v>
+        <v>0.1281</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2882</v>
+        <v>1.2253</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8347</v>
+        <v>0.5849</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5465</v>
+        <v>0.6404</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8295</v>
+        <v>4.4139</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8918</v>
+        <v>3.6082</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9377</v>
+        <v>0.8057</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7614</v>
+        <v>3.7716</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5468</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2147</v>
+        <v>3.2177</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5658</v>
+        <v>3.5553</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1775</v>
+        <v>1.1721</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3883</v>
+        <v>2.3832</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1956</v>
+        <v>0.2164</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8393</v>
+        <v>-0.2682</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8347</v>
+        <v>-0.1048</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0046</v>
+        <v>-0.1634</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4608</v>
+        <v>2.1439</v>
       </c>
       <c r="E4" t="n">
-        <v>2.707</v>
+        <v>2.3469</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2462</v>
+        <v>-0.203</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6252</v>
+        <v>2.6259</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2871</v>
+        <v>1.2867</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3381</v>
+        <v>1.3392</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0597</v>
+        <v>2.052</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3507</v>
+        <v>1.3445</v>
       </c>
       <c r="L4" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7014</v>
+        <v>0.3798</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6472</v>
+        <v>0.2949</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0541</v>
+        <v>0.0849</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7035</v>
+        <v>1.6153</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5206</v>
+        <v>1.9389</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1829</v>
+        <v>-0.3236</v>
       </c>
       <c r="G5" t="n">
-        <v>0.789</v>
+        <v>2.3495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5064</v>
+        <v>0.6918</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2825</v>
+        <v>1.6577</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1547</v>
+        <v>2.2041</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0346</v>
+        <v>0.6927</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1893</v>
+        <v>1.5114</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9436</v>
+        <v>0.1454</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4718</v>
+        <v>-0.0009</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4718</v>
+        <v>0.1463</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7292</v>
+        <v>1.2171</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7168</v>
+        <v>0.873</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0124</v>
+        <v>0.3441</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0267</v>
+        <v>1.3121</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3594</v>
+        <v>0.1565</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3861</v>
+        <v>1.1556</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5479000000000001</v>
+        <v>0.7882</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3693</v>
+        <v>0.5083</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1786</v>
+        <v>0.2799</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0697</v>
+        <v>-0.1594</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0027</v>
+        <v>-0.1939</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6176</v>
+        <v>0.9476</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4417</v>
+        <v>0.4738</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>0.4738</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1605</v>
+        <v>0.345</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4498</v>
+        <v>0.3646</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7107</v>
+        <v>-0.0196</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2249</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6105</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. PEREZ</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8395</v>
+        <v>0.4868</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0395</v>
+        <v>0.4164</v>
       </c>
       <c r="F7" t="n">
-        <v>0.879</v>
+        <v>0.0704</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4564</v>
+        <v>1.4062</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5741</v>
+        <v>0.7552</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8823</v>
+        <v>0.651</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8153</v>
+        <v>2.2071</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6979</v>
+        <v>0.3825</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1174</v>
+        <v>1.8246</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6411</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1238</v>
+        <v>0.3727</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7649</v>
+        <v>-1.1736</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>5.362</v>
+        <v>0.6968</v>
       </c>
       <c r="T7" t="n">
-        <v>3.8834</v>
+        <v>0.5084</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4786</v>
+        <v>0.1884</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.1609</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>-1.1609</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6308</v>
+        <v>-0.095</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1145</v>
+        <v>-1.2481</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4837</v>
+        <v>1.1531</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3485</v>
+        <v>1.3235</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6853</v>
+        <v>-0.0466</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6632</v>
+        <v>1.3701</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2275</v>
+        <v>-0.5575</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7029</v>
+        <v>-0.7207</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5246</v>
+        <v>0.1632</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1211</v>
+        <v>1.881</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0176</v>
+        <v>0.6741</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1387</v>
+        <v>1.2069</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2407</v>
+        <v>-0.0104</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0212</v>
+        <v>0.0834</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2196</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1853</v>
+        <v>-1.8634</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5133</v>
+        <v>-0.8052</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6278</v>
+        <v>-1.8993</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1145</v>
+        <v>1.0941</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4021</v>
+        <v>-0.5504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7517</v>
+        <v>-0.3732</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6504</v>
+        <v>-0.1772</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2197</v>
+        <v>0.0505</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3912</v>
+        <v>0.0582</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8285</v>
+        <v>-0.0077</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8176</v>
+        <v>-0.6009</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3605</v>
+        <v>-0.4314</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1781</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4537</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3049</v>
+        <v>1.3402</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>0.9427</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2516</v>
+        <v>0.3975</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1568</v>
+        <v>-0.2292</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.1568</v>
+        <v>-0.6162</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2772</v>
+        <v>-1.131</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9359</v>
+        <v>-0.5847</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6587</v>
+        <v>-0.5462</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3201</v>
+        <v>-3.6968</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0579</v>
+        <v>-0.8707</v>
       </c>
       <c r="I10" t="n">
-        <v>1.378</v>
+        <v>-2.8261</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5386</v>
+        <v>-1.6484</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7171</v>
+        <v>-0.5828</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1785</v>
+        <v>-1.0656</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8587</v>
+        <v>-2.0483</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6592</v>
+        <v>-0.2879</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1995</v>
+        <v>-1.7604</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1871</v>
+        <v>1.4551</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6261</v>
+        <v>1.1611</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.294</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8639</v>
+        <v>2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7712</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>T. PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4279</v>
+        <v>-1.8816</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6983</v>
+        <v>-2.2009</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7296</v>
+        <v>0.3192</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6991</v>
+        <v>-2.4655</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8789</v>
+        <v>-1.5821</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8202</v>
+        <v>-0.8834</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6315</v>
+        <v>-1.8517</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5786</v>
+        <v>-1.7247</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.053</v>
+        <v>-0.127</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0675</v>
+        <v>-0.6138</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3003</v>
+        <v>0.1426</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7672</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1538</v>
+        <v>2.6537</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0162</v>
+        <v>1.7694</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1376</v>
+        <v>0.8843</v>
       </c>
       <c r="V11" t="n">
-        <v>2.0246</v>
+        <v>-0.9317</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1486</v>
+        <v>-2.0269</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8418</v>
+        <v>-2.808</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6932</v>
+        <v>0.7811</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7619</v>
+        <v>-1.7745</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5223</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2396</v>
+        <v>-1.2518</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4611</v>
+        <v>-2.4935</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.066</v>
+        <v>-2.0864</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0236</v>
+        <v>0.1557</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2299</v>
+        <v>0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2063</v>
+        <v>-0.146</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3702</v>
+        <v>-2.0881</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18</v>
+        <v>0.218</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5503</v>
+        <v>-2.3061</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8862</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1803</v>
+        <v>0.1864</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7063</v>
+        <v>0.6998</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5382</v>
+        <v>2.5201</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6516</v>
+        <v>-1.6339</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3741</v>
+        <v>-0.0849</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0484</v>
+        <v>0.0229</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3257</v>
+        <v>-0.1078</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6089</v>
+        <v>8.302900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>5.062399999999999</v>
+        <v>5.4694</v>
       </c>
       <c r="F14" t="n">
-        <v>2.546399999999999</v>
+        <v>2.833500000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>12.036</v>
+        <v>12.0265</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6934</v>
+        <v>3.7316</v>
       </c>
       <c r="I14" t="n">
-        <v>8.342600000000001</v>
+        <v>8.295</v>
       </c>
       <c r="J14" t="n">
-        <v>14.1049</v>
+        <v>13.8695</v>
       </c>
       <c r="K14" t="n">
-        <v>4.496500000000001</v>
+        <v>4.3859</v>
       </c>
       <c r="L14" t="n">
-        <v>9.608100000000002</v>
+        <v>9.4834</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0687</v>
+        <v>-1.8426</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8033</v>
+        <v>-0.6544000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2654</v>
+        <v>-1.1882</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.6709</v>
+        <v>-5.690899999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R14" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S14" t="n">
-        <v>8.377600000000001</v>
+        <v>9.1052</v>
       </c>
       <c r="T14" t="n">
-        <v>6.0641</v>
+        <v>6.8022</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3135</v>
+        <v>2.3031</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.1342</v>
+        <v>-7.138099999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7718999999999998</v>
+        <v>0.7323999999999997</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.906</v>
+        <v>-7.870399999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6841</v>
+        <v>2.0029</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4729</v>
+        <v>0.4537</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2112</v>
+        <v>1.5492</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.4862</v>
+        <v>-2.4875</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1672</v>
+        <v>-0.1775</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.3189</v>
+        <v>-2.31</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5381</v>
+        <v>-0.5563</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2109</v>
+        <v>0.1961</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.948</v>
+        <v>-1.9312</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4916</v>
+        <v>0.806</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0795</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5733</v>
+        <v>0.8854</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5587</v>
+        <v>0.8037</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3422</v>
+        <v>2.2491</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2165</v>
+        <v>-1.4455</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0915</v>
+        <v>0.0639</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7951</v>
+        <v>1.3762</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7036</v>
+        <v>-1.3123</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6472</v>
+        <v>2.0789</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9382</v>
+        <v>1.5061</v>
       </c>
       <c r="L16" t="n">
-        <v>0.709</v>
+        <v>0.5728</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5557</v>
+        <v>-2.015</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4126</v>
+        <v>-1.8851</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1434</v>
+        <v>-1.5561</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6684</v>
+        <v>-0.5323</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8118</v>
+        <v>-1.0239</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1568</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3982</v>
+        <v>0.5528</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9368</v>
+        <v>0.4912</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5386</v>
+        <v>0.0616</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0698</v>
+        <v>0.0979</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3839</v>
+        <v>0.7901</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3141</v>
+        <v>-0.6922</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1159</v>
+        <v>1.6276</v>
       </c>
       <c r="K17" t="n">
-        <v>1.527</v>
+        <v>0.9201</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5889</v>
+        <v>0.7075</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0461</v>
+        <v>-1.5296</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.903</v>
+        <v>-1.3997</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9665</v>
+        <v>-1.1613</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8861</v>
+        <v>-0.156</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0803</v>
+        <v>-1.0053</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>1.1609</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.0032</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6532</v>
+        <v>-0.4405</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1254</v>
+        <v>0.2156</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7786</v>
+        <v>-0.6561</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3382</v>
+        <v>-0.3329</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1866</v>
+        <v>-0.1862</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0016</v>
+        <v>0.9823</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3398</v>
+        <v>-1.3152</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.1543</v>
+        <v>-1.9499</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3196</v>
+        <v>-1.2319</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8508</v>
+        <v>-0.6747</v>
       </c>
       <c r="E19" t="n">
-        <v>0.297</v>
+        <v>0.1691</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1478</v>
+        <v>-0.8437</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5236</v>
+        <v>-0.5178</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4517</v>
+        <v>-0.451</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0668</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0205</v>
+        <v>-0.0327</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.503</v>
+        <v>-0.4851</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O19" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1418</v>
+        <v>0.0221</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3176</v>
+        <v>0.2018</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4594</v>
+        <v>-0.1797</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6601</v>
+        <v>-1.179</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1155</v>
+        <v>0.4669</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7756</v>
+        <v>-1.6459</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8171</v>
+        <v>-1.0003</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0043</v>
+        <v>-0.4686</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8129</v>
+        <v>-0.5316</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6789</v>
+        <v>-0.5573</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4923</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1866</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.496</v>
+        <v>-0.443</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4966</v>
+        <v>-0.5893</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9994</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1891</v>
+        <v>-0.2973</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0948</v>
+        <v>-0.0653</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0943</v>
+        <v>-0.232</v>
       </c>
       <c r="V20" t="n">
-        <v>1.7997</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7997</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9245</v>
+        <v>-1.2541</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0011</v>
+        <v>0.5505</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9257</v>
+        <v>-1.8046</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0135</v>
+        <v>-0.8046</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4778</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5357</v>
+        <v>-0.7962</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5532</v>
+        <v>1.6578</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1212</v>
+        <v>1.4716</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6744</v>
+        <v>0.1862</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4603</v>
+        <v>-2.4624</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.599</v>
+        <v>-1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
+        <v>-2.2763</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.8211</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.7862</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.6229</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-1.1633</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-1.0186</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.5383</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.4803</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1.2534</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.0927</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-2.3461</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ALIBEGOVIC</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3843</v>
+        <v>-3.2926</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.522</v>
+        <v>-2.2781</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1378</v>
+        <v>-1.0145</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.5739</v>
+        <v>-2.4728</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4313</v>
+        <v>-3.2098</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.1426</v>
+        <v>0.7371</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6802</v>
+        <v>-0.6433</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0674</v>
+        <v>-2.7351</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6127</v>
+        <v>2.0918</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8938</v>
+        <v>-1.8295</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3639</v>
+        <v>-0.4747</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5299</v>
+        <v>-1.3548</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>2.2763</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4189</v>
+        <v>-1.3159</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4265</v>
+        <v>-0.1701</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8454</v>
+        <v>-1.1458</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3817</v>
+        <v>1.6342</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.9497</v>
       </c>
       <c r="X22" t="n">
-        <v>1.3817</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>A. ALIBEGOVIC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7768</v>
+        <v>-4.1244</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3153</v>
+        <v>-5.1515</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4615</v>
+        <v>1.0271</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.445</v>
+        <v>-4.5727</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1886</v>
+        <v>-1.4358</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7436</v>
+        <v>-3.1369</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.583</v>
+        <v>-2.7143</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6992</v>
+        <v>-1.0901</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1162</v>
+        <v>-1.6242</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.862</v>
+        <v>-1.8583</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4894</v>
+        <v>-0.3457</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3726</v>
+        <v>-1.5127</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2683</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8367</v>
+        <v>-1.1695</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2903</v>
+        <v>-0.1609</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.5464</v>
+        <v>-1.0086</v>
       </c>
       <c r="V23" t="n">
-        <v>1.639</v>
+        <v>1.3901</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9604</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>1.3901</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.608699999999999</v>
+        <v>-7.6059</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5464</v>
+        <v>-2.8335</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0623</v>
+        <v>-4.7724</v>
       </c>
       <c r="G24" t="n">
-        <v>-12.0362</v>
+        <v>-12.0268</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.6935</v>
+        <v>-3.7315</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.342699999999999</v>
+        <v>-8.2951</v>
       </c>
       <c r="J24" t="n">
-        <v>2.068599999999999</v>
+        <v>1.842699999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8031000000000001</v>
+        <v>0.6543999999999996</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2655</v>
+        <v>1.1883</v>
       </c>
       <c r="M24" t="n">
-        <v>-14.1047</v>
+        <v>-13.8693</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.4966</v>
+        <v>-4.3861</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.6082</v>
+        <v>-9.483500000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>5.6707</v>
+        <v>5.690699999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R24" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.377699999999999</v>
+        <v>-8.408099999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.3133</v>
+        <v>-2.3032</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.064200000000001</v>
+        <v>-6.1051</v>
       </c>
       <c r="V24" t="n">
-        <v>7.1341</v>
+        <v>7.1381</v>
       </c>
       <c r="W24" t="n">
-        <v>7.906000000000001</v>
+        <v>7.8705</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7719000000000001</v>
+        <v>-0.7323</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104594_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104594_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.870399999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>1.0032</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>1.3901</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104594_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-0.7323</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
